--- a/ANm/aggregate_Eor_results.xlsx
+++ b/ANm/aggregate_Eor_results.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,12 +417,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Maize</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Potato</t>
         </is>
@@ -446,322 +434,322 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>47.51015230362541</v>
+        <v>30.00965219319507</v>
       </c>
       <c r="B3" t="n">
-        <v>50.02187202758569</v>
+        <v>32.52049278997534</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>26.93040049618087</v>
+        <v>16.98795433978385</v>
       </c>
       <c r="B4" t="n">
-        <v>28.35954186034944</v>
+        <v>18.41279804465147</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>18.40243623587548</v>
+        <v>11.57380885566908</v>
       </c>
       <c r="B5" t="n">
-        <v>19.38735338049942</v>
+        <v>12.54991182263825</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>13.79118537162238</v>
+        <v>8.632595654473187</v>
       </c>
       <c r="B6" t="n">
-        <v>14.53923595332602</v>
+        <v>9.367005425769369</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>11.21102513555442</v>
+        <v>6.97536532339646</v>
       </c>
       <c r="B7" t="n">
-        <v>11.82937723225</v>
+        <v>7.575326611388813</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>9.697325277381461</v>
+        <v>5.993649295839812</v>
       </c>
       <c r="B8" t="n">
-        <v>10.24194597703437</v>
+        <v>6.515369249214738</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8.749561603810781</v>
+        <v>5.371525857555416</v>
       </c>
       <c r="B9" t="n">
-        <v>9.249896684597578</v>
+        <v>5.844745158336058</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8.105813883596189</v>
+        <v>4.943531573182535</v>
       </c>
       <c r="B10" t="n">
-        <v>8.577463276359865</v>
+        <v>5.384152553316113</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7.628276690552757</v>
+        <v>4.62250782751659</v>
       </c>
       <c r="B11" t="n">
-        <v>8.079578416418522</v>
+        <v>5.039160163731874</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>7.244141522188026</v>
+        <v>4.362328380811239</v>
       </c>
       <c r="B12" t="n">
-        <v>7.679613688045109</v>
+        <v>4.759805531129113</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6.914771109261537</v>
+        <v>4.138454363529651</v>
       </c>
       <c r="B13" t="n">
-        <v>7.336917974846775</v>
+        <v>4.519519076948825</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6.619536734477403</v>
+        <v>3.937732847632494</v>
       </c>
       <c r="B14" t="n">
-        <v>7.029798416556953</v>
+        <v>4.304067974576843</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6.347317084779021</v>
+        <v>3.753027870741931</v>
       </c>
       <c r="B15" t="n">
-        <v>6.746569615826161</v>
+        <v>4.105737864671947</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>6.092018756072747</v>
+        <v>3.580389571916371</v>
       </c>
       <c r="B16" t="n">
-        <v>6.480837638945874</v>
+        <v>3.920265368504602</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>5.850213250231749</v>
+        <v>3.417559876049566</v>
       </c>
       <c r="B17" t="n">
-        <v>6.229012488272216</v>
+        <v>3.745219022848824</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5.619889464176808</v>
+        <v>3.263183030652741</v>
       </c>
       <c r="B18" t="n">
-        <v>5.988994982899918</v>
+        <v>3.579143998906166</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5.399794600584525</v>
+        <v>3.1163881772277</v>
       </c>
       <c r="B19" t="n">
-        <v>5.759483085023478</v>
+        <v>3.42110992622168</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>5.189085637213481</v>
+        <v>2.976568394811655</v>
       </c>
       <c r="B20" t="n">
-        <v>5.539605130130369</v>
+        <v>3.270471578802775</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4.987144767153083</v>
+        <v>2.843263541713</v>
       </c>
       <c r="B21" t="n">
-        <v>5.32872564278325</v>
+        <v>3.126742008695866</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>4.793481444374819</v>
+        <v>2.716097955536858</v>
       </c>
       <c r="B22" t="n">
-        <v>5.126342299332689</v>
+        <v>2.989525103737468</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>4.607680191510329</v>
+        <v>2.59474716010061</v>
       </c>
       <c r="B23" t="n">
-        <v>4.932031047864979</v>
+        <v>2.858479563398191</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4.429372603359712</v>
+        <v>2.478919921100977</v>
       </c>
       <c r="B24" t="n">
-        <v>4.745416687319543</v>
+        <v>2.73329949737338</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4.258222156080585</v>
+        <v>2.368348433085714</v>
       </c>
       <c r="B25" t="n">
-        <v>4.566156919114452</v>
+        <v>2.613703829137312</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>4.093915805210282</v>
+        <v>2.262782822894844</v>
       </c>
       <c r="B26" t="n">
-        <v>4.39393353980617</v>
+        <v>2.499430372655174</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3.936159193061449</v>
+        <v>2.16198795251537</v>
       </c>
       <c r="B27" t="n">
-        <v>4.228447429383745</v>
+        <v>2.390232397762816</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3.784673784584319</v>
+        <v>2.065741454276818</v>
       </c>
       <c r="B28" t="n">
-        <v>4.069415566727007</v>
+        <v>2.285876528684317</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3.639195042298193</v>
+        <v>1.973832433345801</v>
       </c>
       <c r="B29" t="n">
-        <v>3.916569136615872</v>
+        <v>2.186141363858861</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3.499471169088518</v>
+        <v>1.886060537877251</v>
       </c>
       <c r="B30" t="n">
-        <v>3.769652232671973</v>
+        <v>2.090816492669186</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3.365262168623294</v>
+        <v>1.802235237463397</v>
       </c>
       <c r="B31" t="n">
-        <v>3.628420893074818</v>
+        <v>1.999701736576337</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3.236339089989201</v>
+        <v>1.7221752247669</v>
       </c>
       <c r="B32" t="n">
-        <v>3.492642328813839</v>
+        <v>1.912606522555753</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3.11248338493498</v>
+        <v>1.645707894494952</v>
       </c>
       <c r="B33" t="n">
-        <v>3.362094269222619</v>
+        <v>1.82934933924759</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2.993486338858806</v>
+        <v>1.572668874712022</v>
       </c>
       <c r="B34" t="n">
-        <v>3.236564383991862</v>
+        <v>1.749757248800402</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2.87914855404396</v>
+        <v>1.502901596548455</v>
       </c>
       <c r="B35" t="n">
-        <v>3.115849759114174</v>
+        <v>1.67366543935303</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2.769279472899299</v>
+        <v>1.436256894256758</v>
       </c>
       <c r="B36" t="n">
-        <v>2.999756413941526</v>
+        <v>1.600916809487349</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2.663696933912367</v>
+        <v>1.372592630744412</v>
       </c>
       <c r="B37" t="n">
-        <v>2.888098851744303</v>
+        <v>1.531361579414238</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2.56222675570947</v>
+        <v>1.31177334542023</v>
       </c>
       <c r="B38" t="n">
-        <v>2.780699638974303</v>
+        <v>1.464856925507675</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2.464702346079643</v>
+        <v>1.253669922144492</v>
       </c>
       <c r="B39" t="n">
-        <v>2.677389009973818</v>
+        <v>1.401266635830813</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2.370964333656024</v>
+        <v>1.198159275614752</v>
       </c>
       <c r="B40" t="n">
-        <v>2.578004494753505</v>
+        <v>1.340460784882301</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2.280860220431942</v>
+        <v>1.145124054834194</v>
       </c>
       <c r="B41" t="n">
-        <v>2.482390567953928</v>
+        <v>1.282315426129936</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2.194244053584489</v>
+        <v>1.094452362511736</v>
       </c>
       <c r="B42" t="n">
-        <v>2.390398317431907</v>
+        <v>1.226712301120498</v>
       </c>
     </row>
   </sheetData>
